--- a/results/greedy/UAVs3_GRID13/revenue/UAVs3_GRID13_Greedy.xlsx
+++ b/results/greedy/UAVs3_GRID13/revenue/UAVs3_GRID13_Greedy.xlsx
@@ -547,7 +547,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04157737497007474</v>
+        <v>0.04057554103201255</v>
       </c>
       <c r="C2" t="n">
         <v>33.56053288325084</v>
@@ -605,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.05126883299089968</v>
+        <v>0.05025791696971282</v>
       </c>
       <c r="C2" t="n">
         <v>30.2064913448488</v>
@@ -663,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04401412501465529</v>
+        <v>0.04265837499406189</v>
       </c>
       <c r="C2" t="n">
         <v>31.05281994563968</v>
@@ -721,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04142374999355525</v>
+        <v>0.04019887500908226</v>
       </c>
       <c r="C2" t="n">
         <v>33.46368495632397</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03457016695756465</v>
+        <v>0.03444374998798594</v>
       </c>
       <c r="C2" t="n">
         <v>22.27615283114107</v>
@@ -837,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04023587499978021</v>
+        <v>0.04006304102949798</v>
       </c>
       <c r="C2" t="n">
         <v>29.9077603520466</v>
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04133091599214822</v>
+        <v>0.04112254199571908</v>
       </c>
       <c r="C2" t="n">
         <v>34.84674488549031</v>
@@ -953,7 +953,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03728645900264382</v>
+        <v>0.03536362497834489</v>
       </c>
       <c r="C2" t="n">
         <v>23.37254038344597</v>
@@ -1011,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03468074998818338</v>
+        <v>0.0327547499909997</v>
       </c>
       <c r="C2" t="n">
         <v>27.71918596472182</v>
@@ -1069,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03495075000682846</v>
+        <v>0.03231058298842981</v>
       </c>
       <c r="C2" t="n">
         <v>27.45872006049981</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03821562498342246</v>
+        <v>0.03604250005446374</v>
       </c>
       <c r="C2" t="n">
         <v>30.59162316184377</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03720095800235868</v>
+        <v>0.03595679200952873</v>
       </c>
       <c r="C2" t="n">
         <v>24.13266716616977</v>
@@ -1243,7 +1243,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0472707090084441</v>
+        <v>0.04705858399393037</v>
       </c>
       <c r="C2" t="n">
         <v>32.28236558464513</v>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0311234169639647</v>
+        <v>0.02972016698913649</v>
       </c>
       <c r="C2" t="n">
         <v>28.68824599190022</v>
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03800512501038611</v>
+        <v>0.03624429198680446</v>
       </c>
       <c r="C2" t="n">
         <v>24.07325507030573</v>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03959429101087153</v>
+        <v>0.03839462500764057</v>
       </c>
       <c r="C2" t="n">
         <v>23.84181454886532</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03986291703768075</v>
+        <v>0.03789637499721721</v>
       </c>
       <c r="C2" t="n">
         <v>29.29473815798351</v>
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03358179202768952</v>
+        <v>0.03161416703369468</v>
       </c>
       <c r="C2" t="n">
         <v>29.66979887243331</v>
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04187824996188283</v>
+        <v>0.04045108403079212</v>
       </c>
       <c r="C2" t="n">
         <v>35.20720212460081</v>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04191987501690164</v>
+        <v>0.04123529099160805</v>
       </c>
       <c r="C2" t="n">
         <v>28.64143417533223</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03607045899843797</v>
+        <v>0.03452637494774535</v>
       </c>
       <c r="C2" t="n">
         <v>28.15150807669496</v>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03606208297424018</v>
+        <v>0.03471866599284112</v>
       </c>
       <c r="C2" t="n">
         <v>31.88067348670646</v>
@@ -1823,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04459554102504626</v>
+        <v>0.04379962495295331</v>
       </c>
       <c r="C2" t="n">
         <v>28.74296818951057</v>
@@ -1881,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04765087499981746</v>
+        <v>0.04598954197717831</v>
       </c>
       <c r="C2" t="n">
         <v>27.39717380799102</v>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04042779200244695</v>
+        <v>0.03936875000363216</v>
       </c>
       <c r="C2" t="n">
         <v>32.46263872976168</v>
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04486270796041936</v>
+        <v>0.04423450003378093</v>
       </c>
       <c r="C2" t="n">
         <v>27.84209094367325</v>
@@ -2055,7 +2055,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03215516603086144</v>
+        <v>0.0306902079610154</v>
       </c>
       <c r="C2" t="n">
         <v>29.56686609369418</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.05133354204008356</v>
+        <v>0.0504038329818286</v>
       </c>
       <c r="C2" t="n">
         <v>32.91282487480898</v>
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03562999999849126</v>
+        <v>0.03417104104300961</v>
       </c>
       <c r="C2" t="n">
         <v>24.90026856104738</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04405237501487136</v>
+        <v>0.0420905000064522</v>
       </c>
       <c r="C2" t="n">
         <v>25.90597441330191</v>
@@ -2287,7 +2287,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02814825001405552</v>
+        <v>0.02718516701133922</v>
       </c>
       <c r="C2" t="n">
         <v>26.74419073346318</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03221237502293661</v>
+        <v>0.03038287500385195</v>
       </c>
       <c r="C2" t="n">
         <v>33.39524494624968</v>
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03137462504673749</v>
+        <v>0.02959637501044199</v>
       </c>
       <c r="C2" t="n">
         <v>28.05663511847444</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03911145799793303</v>
+        <v>0.03702008299296722</v>
       </c>
       <c r="C2" t="n">
         <v>32.64272843135961</v>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04659508302574977</v>
+        <v>0.04594495904166251</v>
       </c>
       <c r="C2" t="n">
         <v>23.33521442538495</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04184025002177805</v>
+        <v>0.04057312500663102</v>
       </c>
       <c r="C2" t="n">
         <v>29.65991440435161</v>
@@ -2635,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04005058301845565</v>
+        <v>0.03819649998331442</v>
       </c>
       <c r="C2" t="n">
         <v>30.01081223659089</v>
@@ -2693,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04662866704165936</v>
+        <v>0.04508595902007073</v>
       </c>
       <c r="C2" t="n">
         <v>26.75257998792556</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03368045797105879</v>
+        <v>0.03285329102072865</v>
       </c>
       <c r="C2" t="n">
         <v>31.5707295061172</v>
@@ -2809,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03619095799513161</v>
+        <v>0.03400520799914375</v>
       </c>
       <c r="C2" t="n">
         <v>32.08555282599129</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.05002033297205344</v>
+        <v>0.04826412495458499</v>
       </c>
       <c r="C2" t="n">
         <v>29.7527494018803</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0437294160365127</v>
+        <v>0.04213795799296349</v>
       </c>
       <c r="C2" t="n">
         <v>26.18132375853274</v>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02800704096443951</v>
+        <v>0.02706191700417548</v>
       </c>
       <c r="C2" t="n">
         <v>23.10825166906667</v>
@@ -3041,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03841529099736363</v>
+        <v>0.03640562499640509</v>
       </c>
       <c r="C2" t="n">
         <v>28.09213678398451</v>
@@ -3099,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04679783299798146</v>
+        <v>0.04480412497650832</v>
       </c>
       <c r="C2" t="n">
         <v>32.2405036508032</v>
@@ -3157,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03998233302263543</v>
+        <v>0.03902062500128523</v>
       </c>
       <c r="C2" t="n">
         <v>23.10751516703506</v>
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04289216600591317</v>
+        <v>0.04158483300125226</v>
       </c>
       <c r="C2" t="n">
         <v>30.92404645263468</v>
@@ -3273,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0399907500250265</v>
+        <v>0.03861529100686312</v>
       </c>
       <c r="C2" t="n">
         <v>28.49758496144506</v>
@@ -3331,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04053316701902077</v>
+        <v>0.03938795800786465</v>
       </c>
       <c r="C2" t="n">
         <v>29.90311274947361</v>
@@ -3389,7 +3389,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0306493749958463</v>
+        <v>0.02891591697698459</v>
       </c>
       <c r="C2" t="n">
         <v>24.80864509057644</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03213766601402313</v>
+        <v>0.03032045799773186</v>
       </c>
       <c r="C2" t="n">
         <v>26.70344399150186</v>
@@ -3505,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03656762500759214</v>
+        <v>0.03521054203156382</v>
       </c>
       <c r="C2" t="n">
         <v>27.458347883542</v>
@@ -3563,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04075216699857265</v>
+        <v>0.03888750000623986</v>
       </c>
       <c r="C2" t="n">
         <v>29.15388767568652</v>
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03679383301641792</v>
+        <v>0.03508420899743214</v>
       </c>
       <c r="C2" t="n">
         <v>28.33360744778718</v>
@@ -3679,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03651887498563156</v>
+        <v>0.03525129199260846</v>
       </c>
       <c r="C2" t="n">
         <v>29.6981002777631</v>
@@ -3737,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04299379099393263</v>
+        <v>0.04170795902609825</v>
       </c>
       <c r="C2" t="n">
         <v>24.02661086057657</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04058666701894253</v>
+        <v>0.04008087498368695</v>
       </c>
       <c r="C2" t="n">
         <v>28.59316592062184</v>
@@ -3853,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03368608298478648</v>
+        <v>0.03220170800341293</v>
       </c>
       <c r="C2" t="n">
         <v>28.77293454771415</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04796458303462714</v>
+        <v>0.04596800002036616</v>
       </c>
       <c r="C2" t="n">
         <v>27.24658516375843</v>
@@ -3969,7 +3969,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0371515000006184</v>
+        <v>0.03674866701476276</v>
       </c>
       <c r="C2" t="n">
         <v>26.31293364937044</v>
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04677133297082037</v>
+        <v>0.04547241702675819</v>
       </c>
       <c r="C2" t="n">
         <v>28.49464252557632</v>
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03796887502539903</v>
+        <v>0.03739499999210238</v>
       </c>
       <c r="C2" t="n">
         <v>30.45131782959249</v>
@@ -4143,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03649958403548226</v>
+        <v>0.03511774999788031</v>
       </c>
       <c r="C2" t="n">
         <v>26.73282219871534</v>
@@ -4201,7 +4201,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0478182079968974</v>
+        <v>0.04617574997246265</v>
       </c>
       <c r="C2" t="n">
         <v>26.6894230547568</v>
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.05120912496931851</v>
+        <v>0.04961320798611268</v>
       </c>
       <c r="C2" t="n">
         <v>31.08153587790883</v>
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0378476670011878</v>
+        <v>0.03642462502466515</v>
       </c>
       <c r="C2" t="n">
         <v>27.32935484493474</v>
@@ -4375,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03739554196363315</v>
+        <v>0.03544887498719618</v>
       </c>
       <c r="C2" t="n">
         <v>27.29515705504825</v>
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04015524999704212</v>
+        <v>0.04010445799212903</v>
       </c>
       <c r="C2" t="n">
         <v>27.57292598724822</v>
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03122662496753037</v>
+        <v>0.0298972079763189</v>
       </c>
       <c r="C2" t="n">
         <v>30.47830722661181</v>
@@ -4549,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03379087499342859</v>
+        <v>0.03190812497632578</v>
       </c>
       <c r="C2" t="n">
         <v>27.02870033788232</v>
@@ -4607,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03317266696831211</v>
+        <v>0.0318280829815194</v>
       </c>
       <c r="C2" t="n">
         <v>23.69066263019572</v>
@@ -4665,7 +4665,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03130312502617016</v>
+        <v>0.03110000002197921</v>
       </c>
       <c r="C2" t="n">
         <v>25.67205239388001</v>
@@ -4723,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03529712499585003</v>
+        <v>0.03430304198991507</v>
       </c>
       <c r="C2" t="n">
         <v>25.49003237908198</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04691633401671425</v>
+        <v>0.04560787498485297</v>
       </c>
       <c r="C2" t="n">
         <v>26.66828502473569</v>
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0363181249704212</v>
+        <v>0.03534279204905033</v>
       </c>
       <c r="C2" t="n">
         <v>27.91251590701994</v>
@@ -4897,7 +4897,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03392591699957848</v>
+        <v>0.03360299998894334</v>
       </c>
       <c r="C2" t="n">
         <v>27.19928636593888</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02985629200702533</v>
+        <v>0.02889795799273998</v>
       </c>
       <c r="C2" t="n">
         <v>27.98280735409504</v>
@@ -5013,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04666062496835366</v>
+        <v>0.04599579202476889</v>
       </c>
       <c r="C2" t="n">
         <v>28.87271636804148</v>
@@ -5071,7 +5071,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03275829198537394</v>
+        <v>0.03490179200889543</v>
       </c>
       <c r="C2" t="n">
         <v>29.82001279463268</v>
@@ -5129,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.036027499998454</v>
+        <v>0.03586145804729313</v>
       </c>
       <c r="C2" t="n">
         <v>31.95040864162165</v>
@@ -5187,7 +5187,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03600258298683912</v>
+        <v>0.03610779100563377</v>
       </c>
       <c r="C2" t="n">
         <v>31.03427389133122</v>
@@ -5245,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.039083749987185</v>
+        <v>0.03845449996879324</v>
       </c>
       <c r="C2" t="n">
         <v>30.708469396624</v>
@@ -5303,7 +5303,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03904324996983632</v>
+        <v>0.03870995796751231</v>
       </c>
       <c r="C2" t="n">
         <v>25.074672632395</v>
@@ -5361,7 +5361,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04574091598624364</v>
+        <v>0.04471737495623529</v>
       </c>
       <c r="C2" t="n">
         <v>29.5444617379048</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04280629096319899</v>
+        <v>0.04181808297289535</v>
       </c>
       <c r="C2" t="n">
         <v>22.57527810505344</v>
@@ -5477,7 +5477,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03889324999181554</v>
+        <v>0.03724962496198714</v>
       </c>
       <c r="C2" t="n">
         <v>24.19108910637235</v>
@@ -5535,7 +5535,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02805187500780448</v>
+        <v>0.02761045802617446</v>
       </c>
       <c r="C2" t="n">
         <v>18.10452961413646</v>
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.031467207998503</v>
+        <v>0.0320171249913983</v>
       </c>
       <c r="C2" t="n">
         <v>25.71689017083176</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03842366696335375</v>
+        <v>0.03774879203410819</v>
       </c>
       <c r="C2" t="n">
         <v>31.74613107597972</v>
@@ -5709,7 +5709,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04092266695806757</v>
+        <v>0.04105724999681115</v>
       </c>
       <c r="C2" t="n">
         <v>32.23699478934315</v>
@@ -5767,7 +5767,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04578570794546977</v>
+        <v>0.04518666700460017</v>
       </c>
       <c r="C2" t="n">
         <v>24.6224464002968</v>
@@ -5825,7 +5825,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03490816702833399</v>
+        <v>0.03418783302186057</v>
       </c>
       <c r="C2" t="n">
         <v>29.17633048025832</v>
@@ -5883,7 +5883,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03548295801738277</v>
+        <v>0.03517049999209121</v>
       </c>
       <c r="C2" t="n">
         <v>34.3697448371993</v>
@@ -5941,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04067708301590756</v>
+        <v>0.04074162500910461</v>
       </c>
       <c r="C2" t="n">
         <v>28.7527031709461</v>
@@ -5999,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.05038274999242276</v>
+        <v>0.04861541697755456</v>
       </c>
       <c r="C2" t="n">
         <v>28.68235743920583</v>
@@ -6057,7 +6057,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03359962505055591</v>
+        <v>0.03345899999840185</v>
       </c>
       <c r="C2" t="n">
         <v>28.22625219690298</v>
@@ -6115,7 +6115,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04514262499287724</v>
+        <v>0.04425237502437085</v>
       </c>
       <c r="C2" t="n">
         <v>33.49861529095875</v>
@@ -6173,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03600333305075765</v>
+        <v>0.03500858403276652</v>
       </c>
       <c r="C2" t="n">
         <v>28.07250049013408</v>
@@ -6231,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03479233401594684</v>
+        <v>0.03429745795438066</v>
       </c>
       <c r="C2" t="n">
         <v>20.4322482128596</v>
@@ -6289,7 +6289,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03812283300794661</v>
+        <v>0.03758775000460446</v>
       </c>
       <c r="C2" t="n">
         <v>26.35664037530362</v>

--- a/results/greedy/UAVs3_GRID13/revenue/UAVs3_GRID13_Greedy.xlsx
+++ b/results/greedy/UAVs3_GRID13/revenue/UAVs3_GRID13_Greedy.xlsx
@@ -547,7 +547,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04057554103201255</v>
+        <v>0.04089891701005399</v>
       </c>
       <c r="C2" t="n">
         <v>33.56053288325084</v>
@@ -605,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.05025791696971282</v>
+        <v>0.05089683301048353</v>
       </c>
       <c r="C2" t="n">
         <v>30.2064913448488</v>
@@ -663,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04265837499406189</v>
+        <v>0.04331287497188896</v>
       </c>
       <c r="C2" t="n">
         <v>31.05281994563968</v>
@@ -721,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04019887500908226</v>
+        <v>0.03898566600400954</v>
       </c>
       <c r="C2" t="n">
         <v>33.46368495632397</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03444374998798594</v>
+        <v>0.03417620802065358</v>
       </c>
       <c r="C2" t="n">
         <v>22.27615283114107</v>
@@ -837,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04006304102949798</v>
+        <v>0.0401328339939937</v>
       </c>
       <c r="C2" t="n">
         <v>29.9077603520466</v>
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04112254199571908</v>
+        <v>0.04037762497318909</v>
       </c>
       <c r="C2" t="n">
         <v>34.84674488549031</v>
@@ -953,7 +953,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03536362497834489</v>
+        <v>0.03692554199369624</v>
       </c>
       <c r="C2" t="n">
         <v>23.37254038344597</v>
@@ -1011,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0327547499909997</v>
+        <v>0.0342610829975456</v>
       </c>
       <c r="C2" t="n">
         <v>27.71918596472182</v>
@@ -1069,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03231058298842981</v>
+        <v>0.03434504196047783</v>
       </c>
       <c r="C2" t="n">
         <v>27.45872006049981</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03604250005446374</v>
+        <v>0.03749166696798056</v>
       </c>
       <c r="C2" t="n">
         <v>30.59162316184377</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03595679200952873</v>
+        <v>0.03652491699904203</v>
       </c>
       <c r="C2" t="n">
         <v>24.13266716616977</v>
@@ -1243,7 +1243,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04705858399393037</v>
+        <v>0.04544374998658895</v>
       </c>
       <c r="C2" t="n">
         <v>32.28236558464513</v>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02972016698913649</v>
+        <v>0.03108158300165087</v>
       </c>
       <c r="C2" t="n">
         <v>28.68824599190022</v>
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03624429198680446</v>
+        <v>0.0372937920037657</v>
       </c>
       <c r="C2" t="n">
         <v>24.07325507030573</v>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03839462500764057</v>
+        <v>0.03787854197435081</v>
       </c>
       <c r="C2" t="n">
         <v>23.84181454886532</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03789637499721721</v>
+        <v>0.03938737499993294</v>
       </c>
       <c r="C2" t="n">
         <v>29.29473815798351</v>
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03161416703369468</v>
+        <v>0.03302287502447143</v>
       </c>
       <c r="C2" t="n">
         <v>29.66979887243331</v>
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04045108403079212</v>
+        <v>0.04120879201218486</v>
       </c>
       <c r="C2" t="n">
         <v>35.20720212460081</v>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04123529099160805</v>
+        <v>0.04143149999435991</v>
       </c>
       <c r="C2" t="n">
         <v>28.64143417533223</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03452637494774535</v>
+        <v>0.03555699996650219</v>
       </c>
       <c r="C2" t="n">
         <v>28.15150807669496</v>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03471866599284112</v>
+        <v>0.035563874989748</v>
       </c>
       <c r="C2" t="n">
         <v>31.88067348670646</v>
@@ -1823,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04379962495295331</v>
+        <v>0.0439442089991644</v>
       </c>
       <c r="C2" t="n">
         <v>28.74296818951057</v>
@@ -1881,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04598954197717831</v>
+        <v>0.04488104104530066</v>
       </c>
       <c r="C2" t="n">
         <v>27.39717380799102</v>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03936875000363216</v>
+        <v>0.03918579203309491</v>
       </c>
       <c r="C2" t="n">
         <v>32.46263872976168</v>
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04423450003378093</v>
+        <v>0.04408833401976153</v>
       </c>
       <c r="C2" t="n">
         <v>27.84209094367325</v>
@@ -2055,7 +2055,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0306902079610154</v>
+        <v>0.03130479203537107</v>
       </c>
       <c r="C2" t="n">
         <v>29.56686609369418</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0504038329818286</v>
+        <v>0.05040912498952821</v>
       </c>
       <c r="C2" t="n">
         <v>32.91282487480898</v>
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03417104104300961</v>
+        <v>0.03493154200259596</v>
       </c>
       <c r="C2" t="n">
         <v>24.90026856104738</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0420905000064522</v>
+        <v>0.04347029194468632</v>
       </c>
       <c r="C2" t="n">
         <v>25.90597441330191</v>
@@ -2287,7 +2287,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02718516701133922</v>
+        <v>0.02793691598344594</v>
       </c>
       <c r="C2" t="n">
         <v>26.74419073346318</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03038287500385195</v>
+        <v>0.03177083301125094</v>
       </c>
       <c r="C2" t="n">
         <v>33.39524494624968</v>
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02959637501044199</v>
+        <v>0.03073991602286696</v>
       </c>
       <c r="C2" t="n">
         <v>28.05663511847444</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03702008299296722</v>
+        <v>0.03800829203100875</v>
       </c>
       <c r="C2" t="n">
         <v>32.64272843135961</v>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04594495904166251</v>
+        <v>0.04477379197487608</v>
       </c>
       <c r="C2" t="n">
         <v>23.33521442538495</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04057312500663102</v>
+        <v>0.04114587494404987</v>
       </c>
       <c r="C2" t="n">
         <v>29.65991440435161</v>
@@ -2635,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03819649998331442</v>
+        <v>0.03915370901813731</v>
       </c>
       <c r="C2" t="n">
         <v>30.01081223659089</v>
@@ -2693,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04508595902007073</v>
+        <v>0.04522562498459592</v>
       </c>
       <c r="C2" t="n">
         <v>26.75257998792556</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03285329102072865</v>
+        <v>0.03337658400414512</v>
       </c>
       <c r="C2" t="n">
         <v>31.5707295061172</v>
@@ -2809,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03400520799914375</v>
+        <v>0.03587841603439301</v>
       </c>
       <c r="C2" t="n">
         <v>32.08555282599129</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04826412495458499</v>
+        <v>0.04943174996878952</v>
       </c>
       <c r="C2" t="n">
         <v>29.7527494018803</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04213795799296349</v>
+        <v>0.04345162503886968</v>
       </c>
       <c r="C2" t="n">
         <v>26.18132375853274</v>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02706191700417548</v>
+        <v>0.02746387495426461</v>
       </c>
       <c r="C2" t="n">
         <v>23.10825166906667</v>
@@ -3041,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03640562499640509</v>
+        <v>0.03717649995815009</v>
       </c>
       <c r="C2" t="n">
         <v>28.09213678398451</v>
@@ -3099,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04480412497650832</v>
+        <v>0.04610024997964501</v>
       </c>
       <c r="C2" t="n">
         <v>32.2405036508032</v>
@@ -3157,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03902062500128523</v>
+        <v>0.03855020803166553</v>
       </c>
       <c r="C2" t="n">
         <v>23.10751516703506</v>
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04158483300125226</v>
+        <v>0.0420264580170624</v>
       </c>
       <c r="C2" t="n">
         <v>30.92404645263468</v>
@@ -3273,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03861529100686312</v>
+        <v>0.03911012498429045</v>
       </c>
       <c r="C2" t="n">
         <v>28.49758496144506</v>
@@ -3331,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03938795800786465</v>
+        <v>0.03931412496604025</v>
       </c>
       <c r="C2" t="n">
         <v>29.90311274947361</v>
@@ -3389,7 +3389,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02891591697698459</v>
+        <v>0.02982345799682662</v>
       </c>
       <c r="C2" t="n">
         <v>24.80864509057644</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03032045799773186</v>
+        <v>0.03150250000180677</v>
       </c>
       <c r="C2" t="n">
         <v>26.70344399150186</v>
@@ -3505,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03521054203156382</v>
+        <v>0.06440891703823581</v>
       </c>
       <c r="C2" t="n">
         <v>27.458347883542</v>
@@ -3563,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03888750000623986</v>
+        <v>0.04025841702241451</v>
       </c>
       <c r="C2" t="n">
         <v>29.15388767568652</v>
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03508420899743214</v>
+        <v>0.0348570829955861</v>
       </c>
       <c r="C2" t="n">
         <v>28.33360744778718</v>
@@ -3679,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03525129199260846</v>
+        <v>0.0354312079725787</v>
       </c>
       <c r="C2" t="n">
         <v>29.6981002777631</v>
@@ -3737,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04170795902609825</v>
+        <v>0.04245662502944469</v>
       </c>
       <c r="C2" t="n">
         <v>24.02661086057657</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04008087498368695</v>
+        <v>0.03925991599680856</v>
       </c>
       <c r="C2" t="n">
         <v>28.59316592062184</v>
@@ -3853,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03220170800341293</v>
+        <v>0.03345183399505913</v>
       </c>
       <c r="C2" t="n">
         <v>28.77293454771415</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04596800002036616</v>
+        <v>0.04705674998695031</v>
       </c>
       <c r="C2" t="n">
         <v>27.24658516375843</v>
@@ -3969,7 +3969,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03674866701476276</v>
+        <v>0.03748387499945238</v>
       </c>
       <c r="C2" t="n">
         <v>26.31293364937044</v>
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04547241702675819</v>
+        <v>0.04565870895748958</v>
       </c>
       <c r="C2" t="n">
         <v>28.49464252557632</v>
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03739499999210238</v>
+        <v>0.0366583329741843</v>
       </c>
       <c r="C2" t="n">
         <v>30.45131782959249</v>
@@ -4143,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03511774999788031</v>
+        <v>0.03581245796522126</v>
       </c>
       <c r="C2" t="n">
         <v>26.73282219871534</v>
@@ -4201,7 +4201,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04617574997246265</v>
+        <v>0.04703316697850823</v>
       </c>
       <c r="C2" t="n">
         <v>26.6894230547568</v>
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04961320798611268</v>
+        <v>0.05053558299550787</v>
       </c>
       <c r="C2" t="n">
         <v>31.08153587790883</v>
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03642462502466515</v>
+        <v>0.03788420901400968</v>
       </c>
       <c r="C2" t="n">
         <v>27.32935484493474</v>
@@ -4375,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03544887498719618</v>
+        <v>0.03575741598615423</v>
       </c>
       <c r="C2" t="n">
         <v>27.29515705504825</v>
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04010445799212903</v>
+        <v>0.03815954102901742</v>
       </c>
       <c r="C2" t="n">
         <v>27.57292598724822</v>
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0298972079763189</v>
+        <v>0.03083054098533466</v>
       </c>
       <c r="C2" t="n">
         <v>30.47830722661181</v>
@@ -4549,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03190812497632578</v>
+        <v>0.03316812502453104</v>
       </c>
       <c r="C2" t="n">
         <v>27.02870033788232</v>
@@ -4607,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0318280829815194</v>
+        <v>0.03252025000983849</v>
       </c>
       <c r="C2" t="n">
         <v>23.69066263019572</v>
@@ -4665,7 +4665,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03110000002197921</v>
+        <v>0.03081433300394565</v>
       </c>
       <c r="C2" t="n">
         <v>25.67205239388001</v>
@@ -4723,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03430304198991507</v>
+        <v>0.03517854202073067</v>
       </c>
       <c r="C2" t="n">
         <v>25.49003237908198</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04560787498485297</v>
+        <v>0.04677575000096112</v>
       </c>
       <c r="C2" t="n">
         <v>26.66828502473569</v>
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03534279204905033</v>
+        <v>0.0361100829904899</v>
       </c>
       <c r="C2" t="n">
         <v>27.91251590701994</v>
@@ -4897,7 +4897,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03360299998894334</v>
+        <v>0.03317016700748354</v>
       </c>
       <c r="C2" t="n">
         <v>27.19928636593888</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02889795799273998</v>
+        <v>0.02917508396785706</v>
       </c>
       <c r="C2" t="n">
         <v>27.98280735409504</v>
@@ -5013,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04599579202476889</v>
+        <v>0.04656712501309812</v>
       </c>
       <c r="C2" t="n">
         <v>28.87271636804148</v>
@@ -5071,7 +5071,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03490179200889543</v>
+        <v>0.03239312500227243</v>
       </c>
       <c r="C2" t="n">
         <v>29.82001279463268</v>
@@ -5129,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03586145804729313</v>
+        <v>0.03605225001228973</v>
       </c>
       <c r="C2" t="n">
         <v>31.95040864162165</v>
@@ -5187,7 +5187,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03610779100563377</v>
+        <v>0.03736966702854261</v>
       </c>
       <c r="C2" t="n">
         <v>31.03427389133122</v>
@@ -5245,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03845449996879324</v>
+        <v>0.03896316699683666</v>
       </c>
       <c r="C2" t="n">
         <v>30.708469396624</v>
@@ -5303,7 +5303,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03870995796751231</v>
+        <v>0.03864525002427399</v>
       </c>
       <c r="C2" t="n">
         <v>25.074672632395</v>
@@ -5361,7 +5361,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04471737495623529</v>
+        <v>0.04548920900560915</v>
       </c>
       <c r="C2" t="n">
         <v>29.5444617379048</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04181808297289535</v>
+        <v>0.04327625001315027</v>
       </c>
       <c r="C2" t="n">
         <v>22.57527810505344</v>
@@ -5477,7 +5477,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03724962496198714</v>
+        <v>0.03919700003461912</v>
       </c>
       <c r="C2" t="n">
         <v>24.19108910637235</v>
@@ -5535,7 +5535,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02761045802617446</v>
+        <v>0.0277905419934541</v>
       </c>
       <c r="C2" t="n">
         <v>18.10452961413646</v>
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0320171249913983</v>
+        <v>0.03092295798705891</v>
       </c>
       <c r="C2" t="n">
         <v>25.71689017083176</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03774879203410819</v>
+        <v>0.03803787502693012</v>
       </c>
       <c r="C2" t="n">
         <v>31.74613107597972</v>
@@ -5709,7 +5709,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04105724999681115</v>
+        <v>0.04100270796334371</v>
       </c>
       <c r="C2" t="n">
         <v>32.23699478934315</v>
@@ -5767,7 +5767,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04518666700460017</v>
+        <v>0.04553158296039328</v>
       </c>
       <c r="C2" t="n">
         <v>24.6224464002968</v>
@@ -5825,7 +5825,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03418783302186057</v>
+        <v>0.03432108298875391</v>
       </c>
       <c r="C2" t="n">
         <v>29.17633048025832</v>
@@ -5883,7 +5883,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03517049999209121</v>
+        <v>0.03476045798743144</v>
       </c>
       <c r="C2" t="n">
         <v>34.3697448371993</v>
@@ -5941,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04074162500910461</v>
+        <v>0.04078537499299273</v>
       </c>
       <c r="C2" t="n">
         <v>28.7527031709461</v>
@@ -5999,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04861541697755456</v>
+        <v>0.04909037501784042</v>
       </c>
       <c r="C2" t="n">
         <v>28.68235743920583</v>
@@ -6057,7 +6057,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03345899999840185</v>
+        <v>0.03316912497393787</v>
       </c>
       <c r="C2" t="n">
         <v>28.22625219690298</v>
@@ -6115,7 +6115,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04425237502437085</v>
+        <v>0.04379837500164285</v>
       </c>
       <c r="C2" t="n">
         <v>33.49861529095875</v>
@@ -6173,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03500858403276652</v>
+        <v>0.03499008301878348</v>
       </c>
       <c r="C2" t="n">
         <v>28.07250049013408</v>
@@ -6231,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03429745795438066</v>
+        <v>0.03381537494715303</v>
       </c>
       <c r="C2" t="n">
         <v>20.4322482128596</v>
@@ -6289,7 +6289,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03758775000460446</v>
+        <v>0.03756062500178814</v>
       </c>
       <c r="C2" t="n">
         <v>26.35664037530362</v>
